--- a/artfynd/A 52226-2025 artfynd.xlsx
+++ b/artfynd/A 52226-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>285715</v>
+        <v>84430</v>
       </c>
       <c r="B2" t="n">
-        <v>73685</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>308</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>547859.2860998819</v>
+        <v>547813</v>
       </c>
       <c r="R2" t="n">
-        <v>6955589.511035034</v>
+        <v>6955665</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2008-06-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2008-06-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,12 +759,12 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>i kanten mellan contortaungskog och fin björksumpskog</t>
+          <t>i äldre granskog</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>på ved i klyka vid basen av äldre glasbjörk (24 cm dbh)</t>
+          <t>på gammal fin gran, torrträd (17 cm dbh, 200 år)</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -794,6 +779,117 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Vindkraft 2008 Mörttjärnberget</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>285715</v>
+      </c>
+      <c r="B3" t="n">
+        <v>83299</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>308</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Norr om Tjärnflon, 5 km ONO Räggen, 26 km O Bräcke, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>547859</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6955590</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2008-06-03</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2008-06-03</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>i kanten mellan contortaungskog och fin björksumpskog</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>på ved i klyka vid basen av äldre glasbjörk (24 cm dbh)</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Vindkraft 2008 Mörttjärnberget</t>
         </is>

--- a/artfynd/A 52226-2025 artfynd.xlsx
+++ b/artfynd/A 52226-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Vindkraft 2008 Mörttjärnberget</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84430</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,8 +904,17 @@
           <t>Vindkraft 2008 Mörttjärnberget</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/285715</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>